--- a/Inputs/Recycling_Assumptions.xlsx
+++ b/Inputs/Recycling_Assumptions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Pablo\Programming\R\R Stanford\material-intensity\Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A29DAF-FDF7-45A0-BED1-DF6C0DC11719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4830E9ED-E626-473C-9B04-48839EB38982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{A64A04CB-909E-460D-BA0C-2E868E158A9C}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Downcycling" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Recycling_EOL!$A$1:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Recycling_EOL!$A$1:$H$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
   <si>
     <t>Region</t>
   </si>
@@ -113,6 +113,9 @@
   </si>
   <si>
     <t>Share between Al and Cu: Al 74K, Cu: 29K, by USGS</t>
+  </si>
+  <si>
+    <t>OtherNonFE EOL-RR</t>
   </si>
 </sst>
 </file>
@@ -569,18 +572,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8510DA93-9423-43CF-A326-B3ED535056C0}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22.796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.73046875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.06640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="26.53125" customWidth="1"/>
-    <col min="7" max="7" width="89.9296875" customWidth="1"/>
+    <col min="5" max="5" width="18.06640625" customWidth="1"/>
+    <col min="6" max="7" width="26.53125" customWidth="1"/>
+    <col min="8" max="8" width="89.9296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -594,16 +598,19 @@
         <v>11</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -616,19 +623,23 @@
       <c r="D2" s="7">
         <v>0.61</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="7">
+        <f>+AVERAGE(C2:D2)</f>
+        <v>0.55499999999999994</v>
+      </c>
+      <c r="F2" s="6">
         <f>+B2</f>
         <v>0.75</v>
       </c>
-      <c r="F2" s="6">
+      <c r="G2" s="6">
         <f>29/(74+29)*D2+74/(74+29)*C2</f>
         <v>0.53097087378640773</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -641,19 +652,23 @@
       <c r="D3" s="7">
         <v>0.5</v>
       </c>
-      <c r="E3" s="6">
-        <f t="shared" ref="E3:E10" si="0">+B3</f>
+      <c r="E3" s="7">
+        <f t="shared" ref="E3:E10" si="0">+AVERAGE(C3:D3)</f>
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="F3" s="6">
+        <f t="shared" ref="F3:F10" si="1">+B3</f>
         <v>0.75</v>
       </c>
-      <c r="F3" s="6">
-        <f t="shared" ref="F3:F10" si="1">29/(74+29)*D3+74/(74+29)*C3</f>
+      <c r="G3" s="6">
+        <f t="shared" ref="G3:G10" si="2">29/(74+29)*D3+74/(74+29)*C3</f>
         <v>0.53592233009708745</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -666,17 +681,21 @@
       <c r="D4" s="7">
         <v>0.52</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="7">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="F4" s="6">
         <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="G4" s="6">
+        <f t="shared" si="2"/>
         <v>0.64932038834951455</v>
       </c>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -689,19 +708,23 @@
       <c r="D5" s="8">
         <v>0.4</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="7">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.49</v>
       </c>
       <c r="F5" s="6">
         <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="G5" s="6">
+        <f t="shared" si="2"/>
         <v>0.52932038834951456</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="H5" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -714,19 +737,23 @@
       <c r="D6" s="8">
         <v>0.45</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="7">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.48499999999999999</v>
       </c>
       <c r="F6" s="6">
         <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="G6" s="6">
+        <f t="shared" si="2"/>
         <v>0.50029126213592234</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="H6" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -739,19 +766,23 @@
       <c r="D7" s="11">
         <v>0.47</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.53499999999999992</v>
       </c>
       <c r="F7" s="6">
         <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="G7" s="6">
+        <f t="shared" si="2"/>
         <v>0.56339805825242717</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="H7" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -764,19 +795,23 @@
       <c r="D8" s="11">
         <v>0.47</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="7">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.53499999999999992</v>
       </c>
       <c r="F8" s="6">
         <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="G8" s="6">
+        <f t="shared" si="2"/>
         <v>0.56339805825242717</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -789,19 +824,23 @@
       <c r="D9" s="8">
         <v>0.5</v>
       </c>
-      <c r="E9" s="6">
-        <f t="shared" si="0"/>
-        <v>0.75</v>
+      <c r="E9" s="7">
+        <f>+AVERAGE(C9:D9)</f>
+        <v>0.52500000000000002</v>
       </c>
       <c r="F9" s="6">
         <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+      <c r="G9" s="6">
+        <f t="shared" si="2"/>
         <v>0.53592233009708745</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="H9" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
@@ -814,17 +853,21 @@
       <c r="D10" s="10">
         <v>0.47</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="7">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.53499999999999992</v>
       </c>
       <c r="F10" s="6">
         <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="G10" s="6">
+        <f t="shared" si="2"/>
         <v>0.56339805825242717</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9" xr:uid="{8510DA93-9423-43CF-A326-B3ED535056C0}"/>
+  <autoFilter ref="A1:H9" xr:uid="{8510DA93-9423-43CF-A326-B3ED535056C0}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
